--- a/Team-Data/2012-13/2-7-2012-13.xlsx
+++ b/Team-Data/2012-13/2-7-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>0.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE2" t="n">
         <v>13</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -843,64 +910,64 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
         <v>23</v>
       </c>
       <c r="G3" t="n">
-        <v>0.531</v>
+        <v>0.521</v>
       </c>
       <c r="H3" t="n">
         <v>49.1</v>
       </c>
       <c r="I3" t="n">
-        <v>37</v>
+        <v>36.8</v>
       </c>
       <c r="J3" t="n">
-        <v>80.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.462</v>
+        <v>0.46</v>
       </c>
       <c r="L3" t="n">
         <v>5.5</v>
       </c>
       <c r="M3" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="N3" t="n">
-        <v>0.335</v>
+        <v>0.333</v>
       </c>
       <c r="O3" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P3" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="R3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>31</v>
+      </c>
+      <c r="T3" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="U3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="W3" t="n">
         <v>8.6</v>
-      </c>
-      <c r="S3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="U3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="V3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="W3" t="n">
-        <v>8.699999999999999</v>
       </c>
       <c r="X3" t="n">
         <v>4.1</v>
@@ -909,19 +976,19 @@
         <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="AA3" t="n">
         <v>20</v>
       </c>
       <c r="AB3" t="n">
-        <v>96</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
         <v>15</v>
@@ -930,7 +997,7 @@
         <v>14</v>
       </c>
       <c r="AG3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH3" t="n">
         <v>1</v>
@@ -948,13 +1015,13 @@
         <v>28</v>
       </c>
       <c r="AM3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN3" t="n">
         <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP3" t="n">
         <v>21</v>
@@ -963,19 +1030,19 @@
         <v>6</v>
       </c>
       <c r="AR3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
         <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AW3" t="n">
         <v>4</v>
@@ -993,7 +1060,7 @@
         <v>14</v>
       </c>
       <c r="BB3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC3" t="n">
         <v>15</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -1103,16 +1170,16 @@
         <v>1.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE4" t="n">
         <v>10</v>
       </c>
       <c r="AF4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
         <v>9</v>
@@ -1160,7 +1227,7 @@
         <v>12</v>
       </c>
       <c r="AW4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX4" t="n">
         <v>20</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1312,10 +1379,10 @@
         <v>25</v>
       </c>
       <c r="AM5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO5" t="n">
         <v>2</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E6" t="n">
         <v>29</v>
       </c>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G6" t="n">
-        <v>0.592</v>
+        <v>0.604</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
@@ -1407,37 +1474,37 @@
         <v>35.7</v>
       </c>
       <c r="J6" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="M6" t="n">
-        <v>13.9</v>
+        <v>13.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0.35</v>
+        <v>0.349</v>
       </c>
       <c r="O6" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="P6" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.781</v>
+        <v>0.782</v>
       </c>
       <c r="R6" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="S6" t="n">
-        <v>30.9</v>
+        <v>31.1</v>
       </c>
       <c r="T6" t="n">
-        <v>43.5</v>
+        <v>43.7</v>
       </c>
       <c r="U6" t="n">
         <v>22.8</v>
@@ -1446,40 +1513,40 @@
         <v>14.5</v>
       </c>
       <c r="W6" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X6" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AE6" t="n">
         <v>10</v>
       </c>
       <c r="AF6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG6" t="n">
         <v>10</v>
       </c>
       <c r="AH6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI6" t="n">
         <v>25</v>
@@ -1494,10 +1561,10 @@
         <v>29</v>
       </c>
       <c r="AM6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AN6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO6" t="n">
         <v>9</v>
@@ -1512,10 +1579,10 @@
         <v>8</v>
       </c>
       <c r="AS6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AU6" t="n">
         <v>10</v>
@@ -1533,10 +1600,10 @@
         <v>21</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB6" t="n">
         <v>25</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE7" t="n">
         <v>27</v>
@@ -1679,7 +1746,7 @@
         <v>10</v>
       </c>
       <c r="AN7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO7" t="n">
         <v>16</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-2.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE8" t="n">
         <v>19</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -1935,46 +2002,46 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F9" t="n">
         <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>0.64</v>
+        <v>0.633</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>40.1</v>
+        <v>39.9</v>
       </c>
       <c r="J9" t="n">
-        <v>85.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.471</v>
+        <v>0.468</v>
       </c>
       <c r="L9" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M9" t="n">
         <v>19.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.338</v>
+        <v>0.335</v>
       </c>
       <c r="O9" t="n">
         <v>18</v>
       </c>
       <c r="P9" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="R9" t="n">
         <v>13.6</v>
@@ -1986,37 +2053,37 @@
         <v>45.4</v>
       </c>
       <c r="U9" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="V9" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W9" t="n">
         <v>8.6</v>
       </c>
       <c r="X9" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>104.7</v>
+        <v>104.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AE9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF9" t="n">
         <v>6</v>
@@ -2025,7 +2092,7 @@
         <v>6</v>
       </c>
       <c r="AH9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI9" t="n">
         <v>1</v>
@@ -2034,10 +2101,10 @@
         <v>2</v>
       </c>
       <c r="AK9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM9" t="n">
         <v>17</v>
@@ -2052,7 +2119,7 @@
         <v>3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR9" t="n">
         <v>2</v>
@@ -2067,7 +2134,7 @@
         <v>2</v>
       </c>
       <c r="AV9" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AW9" t="n">
         <v>5</v>
@@ -2079,7 +2146,7 @@
         <v>28</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA9" t="n">
         <v>3</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2310,7 @@
         <v>14</v>
       </c>
       <c r="AT10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU10" t="n">
         <v>24</v>
@@ -2261,7 +2328,7 @@
         <v>19</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>0.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,7 +2456,7 @@
         <v>9</v>
       </c>
       <c r="AH11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI11" t="n">
         <v>5</v>
@@ -2428,7 +2495,7 @@
         <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV11" t="n">
         <v>24</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2635,7 @@
         <v>16</v>
       </c>
       <c r="AG12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
         <v>24</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2811,7 @@
         <v>3</v>
       </c>
       <c r="AE13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF13" t="n">
         <v>8</v>
@@ -2753,7 +2820,7 @@
         <v>8</v>
       </c>
       <c r="AH13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
         <v>29</v>
@@ -2771,10 +2838,10 @@
         <v>16</v>
       </c>
       <c r="AN13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP13" t="n">
         <v>15</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -2944,7 +3011,7 @@
         <v>23</v>
       </c>
       <c r="AK14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
         <v>14</v>
@@ -2974,7 +3041,7 @@
         <v>18</v>
       </c>
       <c r="AU14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV14" t="n">
         <v>11</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E15" t="n">
         <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G15" t="n">
-        <v>0.46</v>
+        <v>0.469</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
@@ -3045,28 +3112,28 @@
         <v>37.2</v>
       </c>
       <c r="J15" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="K15" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L15" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M15" t="n">
         <v>24.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0.351</v>
+        <v>0.354</v>
       </c>
       <c r="O15" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P15" t="n">
         <v>27.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="R15" t="n">
         <v>11.9</v>
@@ -3075,16 +3142,16 @@
         <v>33.1</v>
       </c>
       <c r="T15" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
       <c r="U15" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="V15" t="n">
         <v>15.3</v>
       </c>
       <c r="W15" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X15" t="n">
         <v>5.4</v>
@@ -3096,16 +3163,16 @@
         <v>18.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>102</v>
+        <v>102.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AE15" t="n">
         <v>18</v>
@@ -3123,7 +3190,7 @@
         <v>13</v>
       </c>
       <c r="AJ15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK15" t="n">
         <v>10</v>
@@ -3135,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AO15" t="n">
         <v>4</v>
@@ -3144,7 +3211,7 @@
         <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR15" t="n">
         <v>11</v>
@@ -3156,13 +3223,13 @@
         <v>3</v>
       </c>
       <c r="AU15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AV15" t="n">
         <v>27</v>
       </c>
       <c r="AW15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX15" t="n">
         <v>10</v>
@@ -3174,7 +3241,7 @@
         <v>5</v>
       </c>
       <c r="BA15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB15" t="n">
         <v>6</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>3.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
         <v>8</v>
@@ -3314,7 +3381,7 @@
         <v>30</v>
       </c>
       <c r="AM16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AN16" t="n">
         <v>26</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3578,7 @@
         <v>14</v>
       </c>
       <c r="AR17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS17" t="n">
         <v>19</v>
@@ -3538,7 +3605,7 @@
         <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB17" t="n">
         <v>5</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3718,16 @@
         <v>-0.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF18" t="n">
         <v>14</v>
       </c>
       <c r="AG18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH18" t="n">
         <v>25</v>
@@ -3681,7 +3748,7 @@
         <v>19</v>
       </c>
       <c r="AN18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO18" t="n">
         <v>23</v>
@@ -3699,10 +3766,10 @@
         <v>17</v>
       </c>
       <c r="AT18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -3881,13 +3948,13 @@
         <v>16</v>
       </c>
       <c r="AT19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU19" t="n">
         <v>19</v>
       </c>
       <c r="AV19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW19" t="n">
         <v>15</v>
@@ -3902,7 +3969,7 @@
         <v>2</v>
       </c>
       <c r="BA19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB19" t="n">
         <v>21</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-4.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE20" t="n">
         <v>26</v>
@@ -4027,7 +4094,7 @@
         <v>26</v>
       </c>
       <c r="AH20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
@@ -4069,7 +4136,7 @@
         <v>21</v>
       </c>
       <c r="AV20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW20" t="n">
         <v>29</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4267,7 @@
         <v>28</v>
       </c>
       <c r="AE21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF21" t="n">
         <v>4</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4445,7 +4512,7 @@
         <v>4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA22" t="n">
         <v>9</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-4.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
@@ -4615,7 +4682,7 @@
         <v>7</v>
       </c>
       <c r="AV23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -4743,13 +4810,13 @@
         <v>-3.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE24" t="n">
         <v>19</v>
       </c>
       <c r="AF24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG24" t="n">
         <v>19</v>
@@ -4773,7 +4840,7 @@
         <v>23</v>
       </c>
       <c r="AN24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4794,7 +4861,7 @@
         <v>21</v>
       </c>
       <c r="AU24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV24" t="n">
         <v>3</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -4991,7 +5058,7 @@
         <v>16</v>
       </c>
       <c r="AZ25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA25" t="n">
         <v>27</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -5107,10 +5174,10 @@
         <v>-1.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF26" t="n">
         <v>16</v>
@@ -5164,7 +5231,7 @@
         <v>21</v>
       </c>
       <c r="AW26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX26" t="n">
         <v>20</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5368,7 @@
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI27" t="n">
         <v>20</v>
@@ -5313,7 +5380,7 @@
         <v>23</v>
       </c>
       <c r="AL27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM27" t="n">
         <v>21</v>
@@ -5361,7 +5428,7 @@
         <v>16</v>
       </c>
       <c r="BB27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-1.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5920,7 @@
         <v>17</v>
       </c>
       <c r="AJ30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK30" t="n">
         <v>12</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-4.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6071,7 +6138,7 @@
         <v>20</v>
       </c>
       <c r="AV31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AW31" t="n">
         <v>18</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-7-2012-13</t>
+          <t>2013-02-07</t>
         </is>
       </c>
     </row>
